--- a/project/src/main/resources/static/templates/包边.xlsx
+++ b/project/src/main/resources/static/templates/包边.xlsx
@@ -462,7 +462,6 @@
       <name val="宋体"/>
     </font>
     <font>
-      <u/>
       <color rgb="FF800080"/>
       <sz val="24"/>
       <name val="宋体"/>
@@ -920,20 +919,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R125"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="26.933333333333334" customWidth="1"/>
-    <col min="3" max="3" width="11.066666666666666" customWidth="1"/>
-    <col min="4" max="4" width="97.6" customWidth="1"/>
-    <col min="5" max="10" width="4.933333333333334" customWidth="1"/>
-    <col min="11" max="11" width="9.866666666666667" customWidth="1"/>
-    <col min="12" max="12" width="11.466666666666667" customWidth="1"/>
-    <col min="13" max="15" width="4.933333333333334" customWidth="1"/>
-    <col min="16" max="16" width="6.266666666666667" customWidth="1"/>
-    <col min="17" max="17" width="4.933333333333334" customWidth="1"/>
-    <col min="18" max="18" width="5.733333333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.4" customWidth="1"/>
+    <col min="2" max="2" width="28.533333333333335" customWidth="1"/>
+    <col min="3" max="3" width="11.6" customWidth="1"/>
+    <col min="4" max="4" width="103.86666666666666" customWidth="1"/>
+    <col min="5" max="10" width="5.066666666666666" customWidth="1"/>
+    <col min="11" max="11" width="10.266666666666667" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="15" width="5.066666666666666" customWidth="1"/>
+    <col min="16" max="16" width="6.4" customWidth="1"/>
+    <col min="17" max="17" width="5.066666666666666" customWidth="1"/>
+    <col min="18" max="18" width="5.866666666666666" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -963,16 +962,12 @@
         <v>3</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="3">
-        <f>[40]目录!H10</f>
-      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="5">
-        <f>[40]目录!J10</f>
-      </c>
+      <c r="L2" s="5"/>
     </row>
     <row r="3" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3"/>
@@ -985,58 +980,42 @@
         <v>5</v>
       </c>
       <c r="F3" s="4"/>
-      <c r="G3" s="3">
-        <f>[40]目录!H11</f>
-      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="5">
-        <f>[40]目录!J11</f>
-      </c>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6">
-        <f>[40]目录!H5</f>
-      </c>
+      <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5">
-        <f>[40]目录!H7</f>
-      </c>
+      <c r="D4" s="5"/>
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="4"/>
-      <c r="G4" s="3">
-        <f>[40]目录!H12</f>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="5">
-        <f>[40]目录!J12</f>
-      </c>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" ht="20.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7">
-        <f>[40]目录!H8</f>
-      </c>
+      <c r="B5" s="7"/>
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5">
-        <f>[40]目录!H9</f>
-      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
@@ -1470,7 +1449,6 @@
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="L31"/>
     </row>
     <row r="32" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
@@ -1481,7 +1459,6 @@
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="L32"/>
     </row>
     <row r="33" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
@@ -1492,7 +1469,6 @@
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
-      <c r="L33"/>
     </row>
     <row r="34" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
@@ -1503,7 +1479,6 @@
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
-      <c r="L34"/>
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
@@ -1514,7 +1489,6 @@
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
-      <c r="L35"/>
     </row>
     <row r="36" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
@@ -1525,7 +1499,6 @@
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
-      <c r="L36"/>
     </row>
     <row r="37" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
@@ -1536,7 +1509,6 @@
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
-      <c r="L37"/>
     </row>
     <row r="38" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
@@ -1624,7 +1596,6 @@
       <c r="J43" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L43"/>
     </row>
     <row r="44" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
@@ -1635,7 +1606,6 @@
       </c>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
-      <c r="L44"/>
     </row>
     <row r="45" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
@@ -1646,7 +1616,6 @@
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
-      <c r="L45"/>
     </row>
     <row r="46" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
@@ -1657,7 +1626,6 @@
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
-      <c r="L46"/>
     </row>
     <row r="47" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="20" t="s">
@@ -1683,7 +1651,6 @@
       <c r="J47" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L47"/>
     </row>
     <row r="48" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
@@ -1694,7 +1661,6 @@
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
-      <c r="L48"/>
     </row>
     <row r="49" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
@@ -1734,7 +1700,6 @@
       <c r="J50" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L50"/>
     </row>
     <row r="51" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
@@ -1745,7 +1710,6 @@
       </c>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
-      <c r="L51"/>
     </row>
     <row r="52" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
@@ -1756,7 +1720,6 @@
       </c>
       <c r="C52" s="22"/>
       <c r="D52" s="22"/>
-      <c r="L52"/>
     </row>
     <row r="53" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
@@ -1767,7 +1730,6 @@
       </c>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
-      <c r="L53"/>
     </row>
     <row r="54" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
@@ -1778,7 +1740,6 @@
       </c>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
-      <c r="L54"/>
     </row>
     <row r="55" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
@@ -1789,7 +1750,6 @@
       </c>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
-      <c r="L55"/>
     </row>
     <row r="56" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="20" t="s">
@@ -1815,7 +1775,6 @@
       <c r="J56" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L56"/>
     </row>
     <row r="57" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
@@ -1826,7 +1785,6 @@
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
-      <c r="L57"/>
     </row>
     <row r="58" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
@@ -1837,7 +1795,6 @@
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
-      <c r="L58"/>
     </row>
     <row r="59" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
@@ -1848,7 +1805,6 @@
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
-      <c r="L59"/>
     </row>
     <row r="60" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
@@ -1859,7 +1815,6 @@
       </c>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
-      <c r="L60"/>
     </row>
     <row r="61" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
@@ -1870,7 +1825,6 @@
       </c>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
-      <c r="L61"/>
     </row>
     <row r="62" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
@@ -1881,7 +1835,6 @@
       </c>
       <c r="C62" s="22"/>
       <c r="D62" s="22"/>
-      <c r="L62"/>
     </row>
     <row r="63" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
@@ -1892,7 +1845,6 @@
       </c>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
-      <c r="L63"/>
     </row>
     <row r="64" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
@@ -1903,7 +1855,6 @@
       </c>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
-      <c r="L64"/>
     </row>
     <row r="65" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
@@ -1914,7 +1865,6 @@
       </c>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
-      <c r="L65"/>
     </row>
     <row r="66" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
@@ -1925,7 +1875,6 @@
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
-      <c r="L66"/>
     </row>
     <row r="67" ht="24.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B67" s="20" t="s">
@@ -1951,7 +1900,6 @@
       <c r="J67" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L67"/>
     </row>
     <row r="68" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
@@ -1962,7 +1910,6 @@
       </c>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
-      <c r="L68"/>
     </row>
     <row r="69" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
@@ -1973,7 +1920,6 @@
       </c>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
-      <c r="L69"/>
     </row>
     <row r="70" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
@@ -1984,7 +1930,6 @@
       </c>
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
-      <c r="L70"/>
     </row>
     <row r="71" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
@@ -1995,7 +1940,6 @@
       </c>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
-      <c r="L71"/>
     </row>
     <row r="72" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
@@ -2006,7 +1950,6 @@
       </c>
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
-      <c r="L72"/>
     </row>
     <row r="73" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
@@ -2017,7 +1960,6 @@
       </c>
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
-      <c r="L73"/>
     </row>
     <row r="74" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
@@ -2028,7 +1970,6 @@
       </c>
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
-      <c r="L74"/>
     </row>
     <row r="75" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
@@ -2039,7 +1980,6 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
-      <c r="L75"/>
     </row>
     <row r="76" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
@@ -2050,7 +1990,6 @@
       </c>
       <c r="C76" s="17"/>
       <c r="D76" s="17"/>
-      <c r="L76"/>
     </row>
     <row r="77" ht="24.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
@@ -2061,58 +2000,12 @@
       </c>
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
-      <c r="L77"/>
     </row>
     <row r="78" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="160">
+  <mergeCells count="68">
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:K1"/>
@@ -2181,195 +2074,28 @@
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="K30:L30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="K77:L77"/>
   </mergeCells>
-  <dataValidations count="32">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E10:F30">
-      <formula1>"√,×,无"</formula1>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E10:J42">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E31:J31">
-      <formula1>"A,B,C,D"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E44:J46">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E32:F42">
-      <formula1>"√,×,无"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E48:J49">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E44:F46">
-      <formula1>"√,×,无"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E51:J55">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E48:F49">
-      <formula1>"√,×,无"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E57:J66">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E51:F55">
-      <formula1>"√,×,无"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E68:J80">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E57:F66">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E68:F77">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9:F30">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G11:J11">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G17:J17">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G21:J21">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G23:J23">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G25:J25">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G28:J29">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G32:J32">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G35:J36">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G38:J39">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G44:J44">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G49:J49">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G58:J60">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G63:J63">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G65:J66">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G70:J77">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G9:J9">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H10:I30">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H33:I42">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H45:I46">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H48:I49">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H51:I55">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H57:I66">
-      <formula1>"√,×,无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H68:I77">
-      <formula1>"√,×,无"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9:J42">
+      <formula1>"√,×,/,待"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
